--- a/research/traditional_assets/database/data/bangladesh/bangladesh_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0678</v>
+        <v>0.0183</v>
       </c>
       <c r="E2">
-        <v>0.0722</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-64.32000000000001</v>
+        <v>-61.761</v>
       </c>
       <c r="L2">
-        <v>-0.7965325077399382</v>
+        <v>-0.5577621240856138</v>
       </c>
       <c r="M2">
-        <v>31.9196</v>
+        <v>15.9426</v>
       </c>
       <c r="N2">
-        <v>0.03010686562096188</v>
+        <v>0.02533909754120508</v>
       </c>
       <c r="O2">
-        <v>-0.4962624378109452</v>
+        <v>-0.2581337737407102</v>
       </c>
       <c r="P2">
-        <v>31.9196</v>
+        <v>15.9426</v>
       </c>
       <c r="Q2">
-        <v>0.03010686562096188</v>
+        <v>0.02533909754120508</v>
       </c>
       <c r="R2">
-        <v>-0.4962624378109452</v>
+        <v>-0.2581337737407102</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>998.549</v>
+        <v>363.83</v>
       </c>
       <c r="V2">
-        <v>0.9418407673951387</v>
+        <v>0.5782697840011443</v>
       </c>
       <c r="W2">
-        <v>0.1189318724440347</v>
+        <v>0.06566407529734662</v>
       </c>
       <c r="X2">
-        <v>0.03997416743088113</v>
+        <v>0.07733561159808333</v>
       </c>
       <c r="Y2">
-        <v>0.07895770501315359</v>
+        <v>-0.01167153630073671</v>
       </c>
       <c r="Z2">
-        <v>0.1319487564953103</v>
+        <v>0.205116330764671</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03888723895096426</v>
+        <v>0.06877731560304286</v>
       </c>
       <c r="AC2">
-        <v>-0.03888723895096426</v>
+        <v>-0.06877731560304286</v>
       </c>
       <c r="AD2">
-        <v>1073.94</v>
+        <v>713.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1073.94</v>
+        <v>713.7</v>
       </c>
       <c r="AG2">
-        <v>75.39100000000008</v>
+        <v>349.8700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.503216737342736</v>
+        <v>0.5314736348269006</v>
       </c>
       <c r="AI2">
-        <v>0.8691014736705808</v>
+        <v>0.7285626786443445</v>
       </c>
       <c r="AJ2">
-        <v>0.06638863474054714</v>
+        <v>0.3573602712861579</v>
       </c>
       <c r="AK2">
-        <v>0.3179163451280043</v>
+        <v>0.5681829254429414</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Housing Finance and Investments Limited (DSE:NHFIL)</t>
+          <t>GSP Finance Company (Bangladesh) Limited (DSE:GSPFINANCE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0517</v>
+        <v>-0.157</v>
       </c>
       <c r="E3">
-        <v>0.0559</v>
+        <v>-0.195</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3.76</v>
+        <v>1.26</v>
       </c>
       <c r="L3">
-        <v>0.4590964590964591</v>
+        <v>0.4790874524714829</v>
       </c>
       <c r="M3">
-        <v>3.45</v>
+        <v>0.3376</v>
       </c>
       <c r="N3">
-        <v>0.05058651026392962</v>
+        <v>0.006806451612903226</v>
       </c>
       <c r="O3">
-        <v>0.9175531914893618</v>
+        <v>0.2679365079365079</v>
       </c>
       <c r="P3">
-        <v>3.45</v>
+        <v>0.3376</v>
       </c>
       <c r="Q3">
-        <v>0.05058651026392962</v>
+        <v>0.006806451612903226</v>
       </c>
       <c r="R3">
-        <v>0.9175531914893618</v>
+        <v>0.2679365079365079</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>43.9</v>
+        <v>2.55</v>
       </c>
       <c r="V3">
-        <v>0.6436950146627566</v>
+        <v>0.05141129032258064</v>
       </c>
       <c r="W3">
-        <v>0.1492063492063492</v>
+        <v>0.03214285714285714</v>
       </c>
       <c r="X3">
-        <v>0.03090771850379539</v>
+        <v>0.06196828273233</v>
       </c>
       <c r="Y3">
-        <v>0.1182986307025538</v>
+        <v>-0.02982542558947286</v>
       </c>
       <c r="Z3">
-        <v>0.3756880733944953</v>
+        <v>0.04840787778391312</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03168808731075036</v>
+        <v>0.06312545493018065</v>
       </c>
       <c r="AC3">
-        <v>-0.03168808731075036</v>
+        <v>-0.06312545493018065</v>
       </c>
       <c r="AD3">
-        <v>6.77</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.77</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>-37.13</v>
+        <v>12.95</v>
       </c>
       <c r="AH3">
-        <v>0.09030278778177937</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="AI3">
-        <v>0.2091442693852332</v>
+        <v>0.3112449799196788</v>
       </c>
       <c r="AJ3">
-        <v>-1.195043450273575</v>
+        <v>0.2070343725019984</v>
       </c>
       <c r="AK3">
-        <v>3.220294882914138</v>
+        <v>0.2740740740740741</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Islamic Finance and Investment Limited (DSE:ISLAMICFIN)</t>
+          <t>Bangladesh Finance Limited (DSE:BDFINANCE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00155</v>
+        <v>0.0244</v>
       </c>
       <c r="E4">
-        <v>-0.0194</v>
+        <v>-0.302</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2.37</v>
+        <v>0.469</v>
       </c>
       <c r="L4">
-        <v>0.4438202247191012</v>
+        <v>0.05570071258907363</v>
       </c>
       <c r="M4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="N4">
-        <v>0.03995327102803738</v>
+        <v>0.02164179104477612</v>
       </c>
       <c r="O4">
-        <v>0.7215189873417721</v>
+        <v>3.710021321961621</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>0.03995327102803738</v>
+        <v>0.02164179104477612</v>
       </c>
       <c r="R4">
-        <v>0.7215189873417721</v>
+        <v>3.710021321961621</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>47.7</v>
+        <v>13.7</v>
       </c>
       <c r="V4">
-        <v>1.114485981308411</v>
+        <v>0.1703980099502487</v>
       </c>
       <c r="W4">
-        <v>0.099163179916318</v>
+        <v>0.01221354166666667</v>
       </c>
       <c r="X4">
-        <v>0.03152019917685007</v>
+        <v>0.06405242425650359</v>
       </c>
       <c r="Y4">
-        <v>0.06764298073946792</v>
+        <v>-0.05183888258983693</v>
       </c>
       <c r="Z4">
-        <v>-0.2095761381475667</v>
+        <v>0.1591682419659735</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0321996168563059</v>
+        <v>0.06494495508375295</v>
       </c>
       <c r="AC4">
-        <v>-0.0321996168563059</v>
+        <v>-0.06494495508375295</v>
       </c>
       <c r="AD4">
-        <v>6.87</v>
+        <v>38.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6.87</v>
+        <v>38.1</v>
       </c>
       <c r="AG4">
-        <v>-40.83000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="AH4">
-        <v>0.1383128649083954</v>
+        <v>0.3215189873417721</v>
       </c>
       <c r="AI4">
-        <v>0.2183031458531935</v>
+        <v>0.5059760956175299</v>
       </c>
       <c r="AJ4">
-        <v>-20.72588832487319</v>
+        <v>0.232824427480916</v>
       </c>
       <c r="AK4">
-        <v>2.515711645101663</v>
+        <v>0.3961038961038961</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bangladesh Finance Limited (DSE:BDFINANCE)</t>
+          <t>IPDC Finance Limited (DSE:IPDC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.156</v>
+        <v>0.243</v>
       </c>
       <c r="E5">
-        <v>0.3</v>
+        <v>0.266</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5.76</v>
+        <v>8.65</v>
       </c>
       <c r="L5">
-        <v>0.45</v>
+        <v>0.2993079584775087</v>
       </c>
       <c r="M5">
-        <v>3.16</v>
+        <v>4.41</v>
       </c>
       <c r="N5">
-        <v>0.02791519434628975</v>
+        <v>0.02121212121212121</v>
       </c>
       <c r="O5">
-        <v>0.5486111111111112</v>
+        <v>0.5098265895953757</v>
       </c>
       <c r="P5">
-        <v>3.16</v>
+        <v>4.41</v>
       </c>
       <c r="Q5">
-        <v>0.02791519434628975</v>
+        <v>0.02121212121212121</v>
       </c>
       <c r="R5">
-        <v>0.5486111111111112</v>
+        <v>0.5098265895953757</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>15.5</v>
+        <v>84</v>
       </c>
       <c r="V5">
-        <v>0.1369257950530035</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="W5">
-        <v>0.167930029154519</v>
+        <v>0.1199722607489598</v>
       </c>
       <c r="X5">
-        <v>0.0325652512087332</v>
+        <v>0.06617565064134148</v>
       </c>
       <c r="Y5">
-        <v>0.1353647779457858</v>
+        <v>0.05379661010761831</v>
       </c>
       <c r="Z5">
-        <v>0.2195540308747856</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03402841290566011</v>
+        <v>0.06642996840770748</v>
       </c>
       <c r="AC5">
-        <v>-0.03402841290566011</v>
+        <v>-0.06642996840770748</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>132.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>30</v>
+        <v>132.7</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>48.69999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2094972067039106</v>
+        <v>0.3896065766294773</v>
       </c>
       <c r="AI5">
-        <v>0.398936170212766</v>
+        <v>0.6718987341772151</v>
       </c>
       <c r="AJ5">
-        <v>0.1135473766640564</v>
+        <v>0.1897895557287607</v>
       </c>
       <c r="AK5">
-        <v>0.2428810720268006</v>
+        <v>0.4290748898678414</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GSP Finance Company (Bangladesh) Limited (DSE:GSPFINANCE)</t>
+          <t>IDLC Finance Limited (DSE:IDLC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00162</v>
+        <v>0.00356</v>
       </c>
       <c r="E6">
-        <v>0.0114</v>
+        <v>-0.0398</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3.08</v>
+        <v>18.2</v>
       </c>
       <c r="L6">
-        <v>0.616</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="M6">
-        <v>0.9426</v>
+        <v>5.88</v>
       </c>
       <c r="N6">
-        <v>0.01896579476861167</v>
+        <v>0.03127659574468085</v>
       </c>
       <c r="O6">
-        <v>0.3060389610389611</v>
+        <v>0.3230769230769231</v>
       </c>
       <c r="P6">
-        <v>0.9426</v>
+        <v>5.88</v>
       </c>
       <c r="Q6">
-        <v>0.01896579476861167</v>
+        <v>0.03127659574468085</v>
       </c>
       <c r="R6">
-        <v>0.3060389610389611</v>
+        <v>0.3230769230769231</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.07</v>
+        <v>168.3</v>
       </c>
       <c r="V6">
-        <v>0.08189134808853119</v>
+        <v>0.8952127659574469</v>
       </c>
       <c r="W6">
-        <v>0.0853185595567867</v>
+        <v>0.09494001043296818</v>
       </c>
       <c r="X6">
-        <v>0.03377827164284772</v>
+        <v>0.07317568905766153</v>
       </c>
       <c r="Y6">
-        <v>0.05154028791393898</v>
+        <v>0.02176432137530665</v>
       </c>
       <c r="Z6">
-        <v>0.09889240506329114</v>
+        <v>0.4123422159887799</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0345178777874524</v>
+        <v>0.06692590284483349</v>
       </c>
       <c r="AC6">
-        <v>-0.0345178777874524</v>
+        <v>-0.06692590284483349</v>
       </c>
       <c r="AD6">
-        <v>19.2</v>
+        <v>221.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>19.2</v>
+        <v>221.9</v>
       </c>
       <c r="AG6">
-        <v>15.13</v>
+        <v>53.59999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.2786647314949202</v>
+        <v>0.5413515491583314</v>
       </c>
       <c r="AI6">
-        <v>0.3287671232876712</v>
+        <v>0.5607783674500884</v>
       </c>
       <c r="AJ6">
-        <v>0.2333796082060774</v>
+        <v>0.2218543046357616</v>
       </c>
       <c r="AK6">
-        <v>0.2784833425363519</v>
+        <v>0.2357080035180299</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Delta Brac Housing Finance Corporation Limited (DSE:DBH)</t>
+          <t>First Finance Limited (DSE:FIRSTFIN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1197,98 +1197,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>13.6</v>
-      </c>
-      <c r="L7">
-        <v>0.4963503649635037</v>
+        <v>-17.3</v>
       </c>
       <c r="M7">
-        <v>5.88</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03670411985018727</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.4323529411764706</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>5.88</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03670411985018727</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4323529411764706</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>230.2</v>
+        <v>3.83</v>
       </c>
       <c r="V7">
-        <v>1.436953807740325</v>
+        <v>0.6041009463722398</v>
       </c>
       <c r="W7">
-        <v>0.1894150417827298</v>
+        <v>2.35374149659864</v>
       </c>
       <c r="X7">
-        <v>0.03570788031366211</v>
+        <v>0.08074668631053378</v>
       </c>
       <c r="Y7">
-        <v>0.1537071614690677</v>
+        <v>2.272994810288106</v>
       </c>
       <c r="Z7">
-        <v>-0.479020979020979</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03597362532659041</v>
+        <v>0.06854048677296323</v>
       </c>
       <c r="AC7">
-        <v>-0.03597362532659041</v>
+        <v>-0.06854048677296323</v>
       </c>
       <c r="AD7">
-        <v>92.8</v>
+        <v>11.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>92.8</v>
+        <v>11.2</v>
       </c>
       <c r="AG7">
-        <v>-137.4</v>
+        <v>7.369999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.366798418972332</v>
+        <v>0.6385404789053591</v>
       </c>
       <c r="AI7">
-        <v>0.5290763968072977</v>
+        <v>-0.9105691056910568</v>
       </c>
       <c r="AJ7">
-        <v>-6.026315789473681</v>
+        <v>0.537563822027717</v>
       </c>
       <c r="AK7">
-        <v>2.507299270072993</v>
+        <v>-0.4569125852448852</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1305,7 +1287,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IPDC Finance Limited (DSE:IPDC)</t>
+          <t>United Finance Limited (DSE:UNITEDFIN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1314,10 +1296,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.417</v>
+        <v>0.0122</v>
       </c>
       <c r="E8">
-        <v>0.2</v>
+        <v>-0.135</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1332,28 +1314,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>9.82</v>
+        <v>1.35</v>
       </c>
       <c r="L8">
-        <v>0.3240924092409241</v>
+        <v>0.1614832535885168</v>
       </c>
       <c r="M8">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="N8">
-        <v>0.03156640857653365</v>
+        <v>0.06423611111111112</v>
       </c>
       <c r="O8">
-        <v>0.539714867617108</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="P8">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
-        <v>0.03156640857653365</v>
+        <v>0.06423611111111112</v>
       </c>
       <c r="R8">
-        <v>0.539714867617108</v>
+        <v>1.37037037037037</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1362,55 +1344,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>166.9</v>
+        <v>34.6</v>
       </c>
       <c r="V8">
-        <v>0.9940440738534843</v>
+        <v>1.201388888888889</v>
       </c>
       <c r="W8">
-        <v>0.1387005649717514</v>
+        <v>0.03638814016172507</v>
       </c>
       <c r="X8">
-        <v>0.03687761632220889</v>
+        <v>0.08380625761744881</v>
       </c>
       <c r="Y8">
-        <v>0.1018229486495425</v>
+        <v>-0.04741811745572374</v>
       </c>
       <c r="Z8">
-        <v>2.567796610169495</v>
+        <v>0.1957845433255269</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0366948627051298</v>
+        <v>0.06901414443312248</v>
       </c>
       <c r="AC8">
-        <v>-0.0366948627051298</v>
+        <v>-0.06901414443312248</v>
       </c>
       <c r="AD8">
-        <v>116.9</v>
+        <v>57.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>116.9</v>
+        <v>57.7</v>
       </c>
       <c r="AG8">
-        <v>-50</v>
+        <v>23.1</v>
       </c>
       <c r="AH8">
-        <v>0.4104634831460674</v>
+        <v>0.6670520231213873</v>
       </c>
       <c r="AI8">
-        <v>0.6185185185185186</v>
+        <v>0.6527149321266968</v>
       </c>
       <c r="AJ8">
-        <v>-0.4240882103477523</v>
+        <v>0.4450867052023121</v>
       </c>
       <c r="AK8">
-        <v>-2.262443438914028</v>
+        <v>0.429368029739777</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1427,7 +1409,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IDLC Finance Limited (DSE:IDLC)</t>
+          <t>MIDAS Financing Limited (DSE:MIDASFIN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1436,10 +1418,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0839</v>
+        <v>0.0288</v>
       </c>
       <c r="E9">
-        <v>0.0885</v>
+        <v>0.0378</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1454,28 +1436,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>29.7</v>
+        <v>1.91</v>
       </c>
       <c r="L9">
-        <v>0.368944099378882</v>
+        <v>0.5276243093922651</v>
       </c>
       <c r="M9">
-        <v>7.09</v>
+        <v>0.46</v>
       </c>
       <c r="N9">
-        <v>0.02533952823445318</v>
+        <v>0.02541436464088398</v>
       </c>
       <c r="O9">
-        <v>0.2387205387205387</v>
+        <v>0.2408376963350786</v>
       </c>
       <c r="P9">
-        <v>7.09</v>
+        <v>0.46</v>
       </c>
       <c r="Q9">
-        <v>0.02533952823445318</v>
+        <v>0.02541436464088398</v>
       </c>
       <c r="R9">
-        <v>0.2387205387205387</v>
+        <v>0.2408376963350786</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1484,55 +1466,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>368</v>
+        <v>6.35</v>
       </c>
       <c r="V9">
-        <v>1.315225160829164</v>
+        <v>0.3508287292817679</v>
       </c>
       <c r="W9">
-        <v>0.1760521636040308</v>
+        <v>0.1364285714285714</v>
       </c>
       <c r="X9">
-        <v>0.04131263134081144</v>
+        <v>0.07505664890679795</v>
       </c>
       <c r="Y9">
-        <v>0.1347395322632194</v>
+        <v>0.06137192252177348</v>
       </c>
       <c r="Z9">
-        <v>0.8545647558386413</v>
+        <v>0.1080597014925373</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03871314505969161</v>
+        <v>0.07036596409340401</v>
       </c>
       <c r="AC9">
-        <v>-0.03871314505969161</v>
+        <v>-0.07036596409340401</v>
       </c>
       <c r="AD9">
-        <v>318.9</v>
+        <v>24</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>318.9</v>
+        <v>24</v>
       </c>
       <c r="AG9">
-        <v>-49.10000000000002</v>
+        <v>17.65</v>
       </c>
       <c r="AH9">
-        <v>0.532654083848338</v>
+        <v>0.5700712589073634</v>
       </c>
       <c r="AI9">
-        <v>0.6245593419506463</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="AJ9">
-        <v>-0.2128305158214132</v>
+        <v>0.4937062937062937</v>
       </c>
       <c r="AK9">
-        <v>-0.3443197755960732</v>
+        <v>0.5721231766612642</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1549,7 +1531,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIDAS Financing Limited (DSE:MIDASFIN)</t>
+          <t>Bay Leasing &amp; Investment Limited (DSE:BAYLEASING)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1557,41 +1539,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
       <c r="K10">
-        <v>-4.33</v>
-      </c>
-      <c r="L10">
-        <v>-1.348909657320872</v>
+        <v>-7</v>
       </c>
       <c r="M10">
-        <v>0.137</v>
+        <v>1.19</v>
       </c>
       <c r="N10">
-        <v>0.004612794612794614</v>
+        <v>0.0363914373088685</v>
       </c>
       <c r="O10">
-        <v>-0.03163972286374134</v>
+        <v>-0.17</v>
       </c>
       <c r="P10">
-        <v>0.137</v>
+        <v>1.19</v>
       </c>
       <c r="Q10">
-        <v>0.004612794612794614</v>
+        <v>0.0363914373088685</v>
       </c>
       <c r="R10">
-        <v>-0.03163972286374134</v>
+        <v>-0.17</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1600,55 +1567,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="V10">
-        <v>0.2154882154882155</v>
+        <v>0.4587155963302752</v>
       </c>
       <c r="W10">
-        <v>-0.2366120218579235</v>
+        <v>-0.1876675603217158</v>
       </c>
       <c r="X10">
-        <v>0.03863570352095082</v>
+        <v>0.0796145742893687</v>
       </c>
       <c r="Y10">
-        <v>-0.2752477253788743</v>
+        <v>-0.2672821346110845</v>
       </c>
       <c r="Z10">
-        <v>0.09021922428330521</v>
+        <v>0</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03906133284223691</v>
+        <v>0.07160132496173149</v>
       </c>
       <c r="AC10">
-        <v>-0.03906133284223691</v>
+        <v>-0.07160132496173149</v>
       </c>
       <c r="AD10">
-        <v>25.9</v>
+        <v>54.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>25.9</v>
+        <v>54.9</v>
       </c>
       <c r="AG10">
-        <v>19.5</v>
+        <v>39.9</v>
       </c>
       <c r="AH10">
-        <v>0.4658273381294964</v>
+        <v>0.6267123287671234</v>
       </c>
       <c r="AI10">
-        <v>0.6491228070175439</v>
+        <v>0.7065637065637065</v>
       </c>
       <c r="AJ10">
-        <v>0.3963414634146341</v>
+        <v>0.5495867768595042</v>
       </c>
       <c r="AK10">
-        <v>0.582089552238806</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1665,7 +1632,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United Finance Limited (DSE:UNITEDFIN)</t>
+          <t>Premier Leasing &amp; Finance Limited (DSE:PREMIERLEA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1673,47 +1640,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>-0.0262</v>
-      </c>
-      <c r="E11">
-        <v>-0.0619</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
       <c r="K11">
-        <v>2.95</v>
-      </c>
-      <c r="L11">
-        <v>0.3333333333333334</v>
+        <v>-24.1</v>
       </c>
       <c r="M11">
-        <v>2.73</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N11">
-        <v>0.05896328293736501</v>
+        <v>0.007959641255605381</v>
       </c>
       <c r="O11">
-        <v>0.9254237288135593</v>
+        <v>-0.002946058091286307</v>
       </c>
       <c r="P11">
-        <v>2.73</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q11">
-        <v>0.05896328293736501</v>
+        <v>0.007959641255605381</v>
       </c>
       <c r="R11">
-        <v>0.9254237288135593</v>
+        <v>-0.002946058091286307</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1722,55 +1668,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>58.3</v>
+        <v>23</v>
       </c>
       <c r="V11">
-        <v>1.259179265658747</v>
+        <v>2.57847533632287</v>
       </c>
       <c r="W11">
-        <v>0.08104395604395605</v>
+        <v>-2.42211055276382</v>
       </c>
       <c r="X11">
-        <v>0.04371653625081407</v>
+        <v>0.1613060233884707</v>
       </c>
       <c r="Y11">
-        <v>0.03732741979314198</v>
+        <v>-2.58341657615229</v>
       </c>
       <c r="Z11">
-        <v>0.4402985074626865</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03949278269983229</v>
+        <v>0.07732069116540061</v>
       </c>
       <c r="AC11">
-        <v>-0.03949278269983229</v>
+        <v>-0.07732069116540061</v>
       </c>
       <c r="AD11">
-        <v>63.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>63.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AG11">
-        <v>5.600000000000001</v>
+        <v>48.40000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.5798548094373867</v>
+        <v>0.8889442231075697</v>
       </c>
       <c r="AI11">
-        <v>0.6326732673267327</v>
+        <v>1.18801996672213</v>
       </c>
       <c r="AJ11">
-        <v>0.1078998073217727</v>
+        <v>0.8443824145150035</v>
       </c>
       <c r="AK11">
-        <v>0.1311475409836066</v>
+        <v>1.304582210242587</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1787,7 +1733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bay Leasing &amp; Investment Limited (DSE:BAYLEASING)</t>
+          <t>FAS Finance &amp; Investment Limited (DSE:FASFIN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1795,47 +1741,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.244</v>
-      </c>
-      <c r="E12">
-        <v>0.371</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
       <c r="K12">
-        <v>4.77</v>
-      </c>
-      <c r="L12">
-        <v>0.6662011173184357</v>
+        <v>-45.2</v>
       </c>
       <c r="M12">
-        <v>1.52</v>
+        <v>0.004</v>
       </c>
       <c r="N12">
-        <v>0.0296875</v>
+        <v>0.0004756242568370987</v>
       </c>
       <c r="O12">
-        <v>0.3186582809224319</v>
+        <v>-8.849557522123894e-05</v>
       </c>
       <c r="P12">
-        <v>1.52</v>
+        <v>0.004</v>
       </c>
       <c r="Q12">
-        <v>0.0296875</v>
+        <v>0.0004756242568370987</v>
       </c>
       <c r="R12">
-        <v>0.3186582809224319</v>
+        <v>-8.849557522123894e-05</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1844,512 +1769,60 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="V12">
-        <v>0.259765625</v>
+        <v>1.486325802615933</v>
       </c>
       <c r="W12">
-        <v>0.1423880597014925</v>
+        <v>1.248618784530387</v>
       </c>
       <c r="X12">
-        <v>0.04415352810273445</v>
+        <v>0.1904553434071769</v>
       </c>
       <c r="Y12">
-        <v>0.09823453159875806</v>
+        <v>1.05816344112321</v>
       </c>
       <c r="Z12">
-        <v>0.07181544633901706</v>
+        <v>0</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04144893317184926</v>
+        <v>0.07780615428874865</v>
       </c>
       <c r="AC12">
-        <v>-0.04144893317184926</v>
+        <v>-0.07780615428874865</v>
       </c>
       <c r="AD12">
-        <v>72.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>72.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="AG12">
-        <v>59.60000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="AH12">
-        <v>0.5874294923448832</v>
+        <v>0.9112026185196918</v>
       </c>
       <c r="AI12">
-        <v>0.6615245009074411</v>
+        <v>8.460784313725487</v>
       </c>
       <c r="AJ12">
-        <v>0.5379061371841155</v>
+        <v>0.8977010096095366</v>
       </c>
       <c r="AK12">
-        <v>0.6150670794633644</v>
+        <v>-32.08695652173917</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>First Finance Limited (DSE:FIRSTFIN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>-0</v>
-      </c>
-      <c r="H13">
-        <v>-0</v>
-      </c>
-      <c r="I13">
-        <v>-0</v>
-      </c>
-      <c r="J13">
-        <v>-0</v>
-      </c>
-      <c r="K13">
-        <v>-15.9</v>
-      </c>
-      <c r="L13">
-        <v>1.292682926829268</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>4.57</v>
-      </c>
-      <c r="V13">
-        <v>0.4908700322234157</v>
-      </c>
-      <c r="W13">
-        <v>-1.859649122807017</v>
-      </c>
-      <c r="X13">
-        <v>0.04527509167262934</v>
-      </c>
-      <c r="Y13">
-        <v>-1.904924214479647</v>
-      </c>
-      <c r="Z13">
-        <v>-0.6630727762803234</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.04180718603587599</v>
-      </c>
-      <c r="AC13">
-        <v>-0.04180718603587599</v>
-      </c>
-      <c r="AD13">
-        <v>14.3</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>14.3</v>
-      </c>
-      <c r="AG13">
-        <v>9.73</v>
-      </c>
-      <c r="AH13">
-        <v>0.6056755612028801</v>
-      </c>
-      <c r="AI13">
-        <v>2.057553956834532</v>
-      </c>
-      <c r="AJ13">
-        <v>0.511029411764706</v>
-      </c>
-      <c r="AK13">
-        <v>4.088235294117646</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Premier Leasing &amp; Finance Limited (DSE:PREMIERLEA)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>-0</v>
-      </c>
-      <c r="H14">
-        <v>-0</v>
-      </c>
-      <c r="I14">
-        <v>-0</v>
-      </c>
-      <c r="J14">
-        <v>-0</v>
-      </c>
-      <c r="K14">
-        <v>-14.7</v>
-      </c>
-      <c r="L14">
-        <v>1.105263157894737</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>24.9</v>
-      </c>
-      <c r="V14">
-        <v>1.992</v>
-      </c>
-      <c r="W14">
-        <v>-0.6</v>
-      </c>
-      <c r="X14">
-        <v>0.08191580839338314</v>
-      </c>
-      <c r="Y14">
-        <v>-0.6819158083933832</v>
-      </c>
-      <c r="Z14">
-        <v>-0.2440814828408883</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.04638269981915875</v>
-      </c>
-      <c r="AC14">
-        <v>-0.04638269981915875</v>
-      </c>
-      <c r="AD14">
-        <v>65</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>65</v>
-      </c>
-      <c r="AG14">
-        <v>40.1</v>
-      </c>
-      <c r="AH14">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="AI14">
-        <v>0.808457711442786</v>
-      </c>
-      <c r="AJ14">
-        <v>0.7623574144486692</v>
-      </c>
-      <c r="AK14">
-        <v>0.7225225225225226</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FAS Finance &amp; Investment Limited (DSE:FASFIN)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>-0</v>
-      </c>
-      <c r="H15">
-        <v>-0</v>
-      </c>
-      <c r="I15">
-        <v>-0</v>
-      </c>
-      <c r="J15">
-        <v>-0</v>
-      </c>
-      <c r="K15">
-        <v>-23.3</v>
-      </c>
-      <c r="L15">
-        <v>1.059090909090909</v>
-      </c>
-      <c r="M15">
-        <v>-0</v>
-      </c>
-      <c r="N15">
-        <v>-0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>-0</v>
-      </c>
-      <c r="Q15">
-        <v>-0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>14.8</v>
-      </c>
-      <c r="V15">
-        <v>1.213114754098361</v>
-      </c>
-      <c r="W15">
-        <v>2.008620689655173</v>
-      </c>
-      <c r="X15">
-        <v>0.1077850455386022</v>
-      </c>
-      <c r="Y15">
-        <v>1.90083564411657</v>
-      </c>
-      <c r="Z15">
-        <v>-0.3369065849923431</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.0491375237068197</v>
-      </c>
-      <c r="AC15">
-        <v>-0.0491375237068197</v>
-      </c>
-      <c r="AD15">
-        <v>95</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>95</v>
-      </c>
-      <c r="AG15">
-        <v>80.2</v>
-      </c>
-      <c r="AH15">
-        <v>0.8861940298507462</v>
-      </c>
-      <c r="AI15">
-        <v>1.615646258503401</v>
-      </c>
-      <c r="AJ15">
-        <v>0.8679653679653679</v>
-      </c>
-      <c r="AK15">
-        <v>1.822727272727273</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>International Leasing and Financial Services Limited (DSE:ILFSL)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>-0</v>
-      </c>
-      <c r="H16">
-        <v>-0</v>
-      </c>
-      <c r="I16">
-        <v>-0</v>
-      </c>
-      <c r="J16">
-        <v>-0</v>
-      </c>
-      <c r="K16">
-        <v>-81.90000000000001</v>
-      </c>
-      <c r="L16">
-        <v>1.355960264900662</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="V16">
-        <v>0.0005232558139534884</v>
-      </c>
-      <c r="W16">
-        <v>-2.4375</v>
-      </c>
-      <c r="X16">
-        <v>0.1145093163280737</v>
-      </c>
-      <c r="Y16">
-        <v>-2.552009316328073</v>
-      </c>
-      <c r="Z16">
-        <v>-0.3676649622595569</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.04931300283466442</v>
-      </c>
-      <c r="AC16">
-        <v>-0.04931300283466442</v>
-      </c>
-      <c r="AD16">
-        <v>145.5</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>145.5</v>
-      </c>
-      <c r="AG16">
-        <v>145.491</v>
-      </c>
-      <c r="AH16">
-        <v>0.8942839582052858</v>
-      </c>
-      <c r="AI16">
-        <v>-0.6217948717948718</v>
-      </c>
-      <c r="AJ16">
-        <v>0.8942781100368183</v>
-      </c>
-      <c r="AK16">
-        <v>-0.6217324974680462</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0183</v>
+        <v>-0.0265</v>
       </c>
       <c r="E2">
-        <v>-0.08740000000000001</v>
+        <v>-0.0541</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.02521491957848031</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.02481974486966167</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.0230865224625624</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.02026111009048811</v>
       </c>
       <c r="K2">
-        <v>-61.761</v>
+        <v>4.990000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.5577621240856138</v>
+        <v>0.03459511924570161</v>
       </c>
       <c r="M2">
-        <v>15.9426</v>
+        <v>23.502</v>
       </c>
       <c r="N2">
-        <v>0.02533909754120508</v>
+        <v>0.02699052540913006</v>
       </c>
       <c r="O2">
-        <v>-0.2581337737407102</v>
+        <v>4.709819639278556</v>
       </c>
       <c r="P2">
-        <v>15.9426</v>
+        <v>23.502</v>
       </c>
       <c r="Q2">
-        <v>0.02533909754120508</v>
+        <v>0.02699052540913006</v>
       </c>
       <c r="R2">
-        <v>-0.2581337737407102</v>
+        <v>4.709819639278556</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>363.83</v>
+        <v>789.77</v>
       </c>
       <c r="V2">
-        <v>0.5782697840011443</v>
+        <v>0.9069997128911857</v>
       </c>
       <c r="W2">
-        <v>0.06566407529734662</v>
+        <v>0.05339942930351736</v>
       </c>
       <c r="X2">
-        <v>0.07733561159808333</v>
+        <v>0.08797529570367918</v>
       </c>
       <c r="Y2">
-        <v>-0.01167153630073671</v>
+        <v>-0.03457586640016182</v>
       </c>
       <c r="Z2">
-        <v>0.205116330764671</v>
+        <v>0.1546279024892262</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06877731560304286</v>
+        <v>0.0771853239320337</v>
       </c>
       <c r="AC2">
-        <v>-0.06877731560304286</v>
+        <v>-0.0771853239320337</v>
       </c>
       <c r="AD2">
-        <v>713.7</v>
+        <v>1100.54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>713.7</v>
+        <v>1100.54</v>
       </c>
       <c r="AG2">
-        <v>349.8700000000001</v>
+        <v>310.77</v>
       </c>
       <c r="AH2">
-        <v>0.5314736348269006</v>
+        <v>0.5582841692495777</v>
       </c>
       <c r="AI2">
-        <v>0.7285626786443445</v>
+        <v>0.6792031302072404</v>
       </c>
       <c r="AJ2">
-        <v>0.3573602712861579</v>
+        <v>0.2630255941499086</v>
       </c>
       <c r="AK2">
-        <v>0.5681829254429414</v>
+        <v>0.3741647302454941</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.108</v>
+      </c>
+      <c r="AO2">
+        <v>18</v>
+      </c>
+      <c r="AQ2">
+        <v>30.83333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GSP Finance Company (Bangladesh) Limited (DSE:GSPFINANCE)</t>
+          <t>Information Technology Consultants Limited (DSE:ITC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.157</v>
+        <v>0.079</v>
       </c>
       <c r="E3">
-        <v>-0.195</v>
+        <v>0.208</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3135344827586207</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3086206896551724</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.2870689655172414</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.2776222870992618</v>
       </c>
       <c r="K3">
-        <v>1.26</v>
+        <v>3.03</v>
       </c>
       <c r="L3">
-        <v>0.4790874524714829</v>
+        <v>0.2612068965517241</v>
       </c>
       <c r="M3">
-        <v>0.3376</v>
+        <v>0.716</v>
       </c>
       <c r="N3">
-        <v>0.006806451612903226</v>
+        <v>0.01645977011494253</v>
       </c>
       <c r="O3">
-        <v>0.2679365079365079</v>
+        <v>0.2363036303630363</v>
       </c>
       <c r="P3">
-        <v>0.3376</v>
+        <v>0.716</v>
       </c>
       <c r="Q3">
-        <v>0.006806451612903226</v>
+        <v>0.01645977011494253</v>
       </c>
       <c r="R3">
-        <v>0.2679365079365079</v>
+        <v>0.2363036303630363</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,61 +764,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>0.05141129032258064</v>
+        <v>0.05195402298850575</v>
       </c>
       <c r="W3">
-        <v>0.03214285714285714</v>
+        <v>0.1346666666666667</v>
       </c>
       <c r="X3">
-        <v>0.06196828273233</v>
+        <v>0.06636923637668771</v>
       </c>
       <c r="Y3">
-        <v>-0.02982542558947286</v>
+        <v>0.06829743028997895</v>
       </c>
       <c r="Z3">
-        <v>0.04840787778391312</v>
+        <v>0.5220522052205221</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1449333271985346</v>
       </c>
       <c r="AB3">
-        <v>0.06312545493018065</v>
+        <v>0.0663487409151424</v>
       </c>
       <c r="AC3">
-        <v>-0.06312545493018065</v>
+        <v>0.07858458628339218</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>1.82</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>1.82</v>
       </c>
       <c r="AG3">
-        <v>12.95</v>
+        <v>-0.4399999999999997</v>
       </c>
       <c r="AH3">
-        <v>0.2380952380952381</v>
+        <v>0.04015887025595764</v>
       </c>
       <c r="AI3">
-        <v>0.3112449799196788</v>
+        <v>0.07362459546925566</v>
       </c>
       <c r="AJ3">
-        <v>0.2070343725019984</v>
+        <v>-0.01021830004644681</v>
       </c>
       <c r="AK3">
-        <v>0.2740740740740741</v>
+        <v>-0.01959038290293855</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.108</v>
+      </c>
+      <c r="AO3">
+        <v>18</v>
+      </c>
+      <c r="AQ3">
+        <v>30.83333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bangladesh Finance Limited (DSE:BDFINANCE)</t>
+          <t>Islamic Finance and Investment Limited (DSE:ISLAMICFIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +844,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0244</v>
-      </c>
-      <c r="E4">
-        <v>-0.302</v>
+        <v>-0.459</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.469</v>
+        <v>-2.44</v>
       </c>
       <c r="L4">
-        <v>0.05570071258907363</v>
+        <v>-12.2</v>
       </c>
       <c r="M4">
-        <v>1.74</v>
+        <v>0.715</v>
       </c>
       <c r="N4">
-        <v>0.02164179104477612</v>
+        <v>0.02837301587301587</v>
       </c>
       <c r="O4">
-        <v>3.710021321961621</v>
+        <v>-0.2930327868852459</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>0.715</v>
       </c>
       <c r="Q4">
-        <v>0.02164179104477612</v>
+        <v>0.02837301587301587</v>
       </c>
       <c r="R4">
-        <v>3.710021321961621</v>
+        <v>-0.2930327868852459</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="V4">
-        <v>0.1703980099502487</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="W4">
-        <v>0.01221354166666667</v>
+        <v>-0.122</v>
       </c>
       <c r="X4">
-        <v>0.06405242425650359</v>
+        <v>0.06939417202177656</v>
       </c>
       <c r="Y4">
-        <v>-0.05183888258983693</v>
+        <v>-0.1913941720217766</v>
       </c>
       <c r="Z4">
-        <v>0.1591682419659735</v>
+        <v>0.03944773175542406</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06494495508375295</v>
+        <v>0.06879718286546163</v>
       </c>
       <c r="AC4">
-        <v>-0.06494495508375295</v>
+        <v>-0.06879718286546163</v>
       </c>
       <c r="AD4">
-        <v>38.1</v>
+        <v>5.12</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>38.1</v>
+        <v>5.12</v>
       </c>
       <c r="AG4">
-        <v>24.4</v>
+        <v>-8.379999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.3215189873417721</v>
+        <v>0.1688654353562005</v>
       </c>
       <c r="AI4">
-        <v>0.5059760956175299</v>
+        <v>0.2519685039370079</v>
       </c>
       <c r="AJ4">
-        <v>0.232824427480916</v>
+        <v>-0.4982164090368608</v>
       </c>
       <c r="AK4">
-        <v>0.3961038961038961</v>
+        <v>-1.228739002932551</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IPDC Finance Limited (DSE:IPDC)</t>
+          <t>National Housing Finance PLC (DSE:NHFIL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.243</v>
+        <v>-0.0273</v>
       </c>
       <c r="E5">
-        <v>0.266</v>
+        <v>-0.0395</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>8.65</v>
+        <v>1.81</v>
       </c>
       <c r="L5">
-        <v>0.2993079584775087</v>
+        <v>0.3755186721991701</v>
       </c>
       <c r="M5">
-        <v>4.41</v>
+        <v>1.6</v>
       </c>
       <c r="N5">
-        <v>0.02121212121212121</v>
+        <v>0.03587443946188341</v>
       </c>
       <c r="O5">
-        <v>0.5098265895953757</v>
+        <v>0.8839779005524863</v>
       </c>
       <c r="P5">
-        <v>4.41</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>0.02121212121212121</v>
+        <v>0.03587443946188341</v>
       </c>
       <c r="R5">
-        <v>0.5098265895953757</v>
+        <v>0.8839779005524863</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>84</v>
+        <v>10.4</v>
       </c>
       <c r="V5">
-        <v>0.404040404040404</v>
+        <v>0.2331838565022422</v>
       </c>
       <c r="W5">
-        <v>0.1199722607489598</v>
+        <v>0.08116591928251121</v>
       </c>
       <c r="X5">
-        <v>0.06617565064134148</v>
+        <v>0.07445498755997074</v>
       </c>
       <c r="Y5">
-        <v>0.05379661010761831</v>
+        <v>0.006710931722540475</v>
       </c>
       <c r="Z5">
-        <v>1.307692307692308</v>
+        <v>0.288622754491018</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06642996840770748</v>
+        <v>0.07360089980147753</v>
       </c>
       <c r="AC5">
-        <v>-0.06642996840770748</v>
+        <v>-0.07360089980147753</v>
       </c>
       <c r="AD5">
-        <v>132.7</v>
+        <v>21.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>132.7</v>
+        <v>21.1</v>
       </c>
       <c r="AG5">
-        <v>48.69999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="AH5">
-        <v>0.3896065766294773</v>
+        <v>0.3211567732115677</v>
       </c>
       <c r="AI5">
-        <v>0.6718987341772151</v>
+        <v>0.5059952038369304</v>
       </c>
       <c r="AJ5">
-        <v>0.1897895557287607</v>
+        <v>0.1934900542495479</v>
       </c>
       <c r="AK5">
-        <v>0.4290748898678414</v>
+        <v>0.34185303514377</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDLC Finance Limited (DSE:IDLC)</t>
+          <t>Bangladesh Finance Limited (DSE:BDFINANCE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00356</v>
+        <v>-0.0008899999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.0398</v>
+        <v>-0.159</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>18.2</v>
+        <v>1.34</v>
       </c>
       <c r="L6">
-        <v>0.3095238095238095</v>
+        <v>0.2504672897196262</v>
       </c>
       <c r="M6">
-        <v>5.88</v>
+        <v>2.33</v>
       </c>
       <c r="N6">
-        <v>0.03127659574468085</v>
+        <v>0.03077939233817701</v>
       </c>
       <c r="O6">
-        <v>0.3230769230769231</v>
+        <v>1.738805970149254</v>
       </c>
       <c r="P6">
-        <v>5.88</v>
+        <v>2.33</v>
       </c>
       <c r="Q6">
-        <v>0.03127659574468085</v>
+        <v>0.03077939233817701</v>
       </c>
       <c r="R6">
-        <v>0.3230769230769231</v>
+        <v>1.738805970149254</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>168.3</v>
+        <v>14.1</v>
       </c>
       <c r="V6">
-        <v>0.8952127659574469</v>
+        <v>0.1862615587846763</v>
       </c>
       <c r="W6">
-        <v>0.09494001043296818</v>
+        <v>0.04213836477987422</v>
       </c>
       <c r="X6">
-        <v>0.07317568905766153</v>
+        <v>0.07583871691085037</v>
       </c>
       <c r="Y6">
-        <v>0.02176432137530665</v>
+        <v>-0.03370035213097615</v>
       </c>
       <c r="Z6">
-        <v>0.4123422159887799</v>
+        <v>0.09519572953736653</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06692590284483349</v>
+        <v>0.07440928908818746</v>
       </c>
       <c r="AC6">
-        <v>-0.06692590284483349</v>
+        <v>-0.07440928908818746</v>
       </c>
       <c r="AD6">
-        <v>221.9</v>
+        <v>41.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>221.9</v>
+        <v>41.4</v>
       </c>
       <c r="AG6">
-        <v>53.59999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="AH6">
-        <v>0.5413515491583314</v>
+        <v>0.3535439795046968</v>
       </c>
       <c r="AI6">
-        <v>0.5607783674500884</v>
+        <v>0.553475935828877</v>
       </c>
       <c r="AJ6">
-        <v>0.2218543046357616</v>
+        <v>0.2650485436893203</v>
       </c>
       <c r="AK6">
-        <v>0.2357080035180299</v>
+        <v>0.4497528830313015</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Finance Limited (DSE:FIRSTFIN)</t>
+          <t>IPDC Finance Limited (DSE:IPDC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1197,80 +1206,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.08779999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.0277</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
-        <v>-17.3</v>
+        <v>4.19</v>
+      </c>
+      <c r="L7">
+        <v>0.2240641711229947</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>3.37</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.01728205128205128</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.8042959427207637</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>3.37</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01728205128205128</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.8042959427207637</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>3.83</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V7">
-        <v>0.6041009463722398</v>
+        <v>0.5123076923076924</v>
       </c>
       <c r="W7">
-        <v>2.35374149659864</v>
+        <v>0.06466049382716051</v>
       </c>
       <c r="X7">
-        <v>0.08074668631053378</v>
+        <v>0.07678631370527823</v>
       </c>
       <c r="Y7">
-        <v>2.272994810288106</v>
+        <v>-0.01212581987811773</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>0.1647577092511013</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06854048677296323</v>
+        <v>0.07491979414741609</v>
       </c>
       <c r="AC7">
-        <v>-0.06854048677296323</v>
+        <v>-0.07491979414741609</v>
       </c>
       <c r="AD7">
-        <v>11.2</v>
+        <v>116.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.2</v>
+        <v>116.5</v>
       </c>
       <c r="AG7">
-        <v>7.369999999999999</v>
+        <v>16.59999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.6385404789053591</v>
+        <v>0.3739967897271268</v>
       </c>
       <c r="AI7">
-        <v>-0.9105691056910568</v>
+        <v>0.660805445263755</v>
       </c>
       <c r="AJ7">
-        <v>0.537563822027717</v>
+        <v>0.07844990548204156</v>
       </c>
       <c r="AK7">
-        <v>-0.4569125852448852</v>
+        <v>0.2172774869109947</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1287,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Finance Limited (DSE:UNITEDFIN)</t>
+          <t>Bay Leasing &amp; Investment Limited (DSE:BAYLEASING)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1295,47 +1328,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0122</v>
-      </c>
-      <c r="E8">
-        <v>-0.135</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
       <c r="K8">
-        <v>1.35</v>
-      </c>
-      <c r="L8">
-        <v>0.1614832535885168</v>
+        <v>-10.2</v>
       </c>
       <c r="M8">
-        <v>1.85</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N8">
-        <v>0.06423611111111112</v>
+        <v>0.002801302931596091</v>
       </c>
       <c r="O8">
-        <v>1.37037037037037</v>
+        <v>-0.008431372549019607</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q8">
-        <v>0.06423611111111112</v>
+        <v>0.002801302931596091</v>
       </c>
       <c r="R8">
-        <v>1.37037037037037</v>
+        <v>-0.008431372549019607</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1344,55 +1356,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>34.6</v>
+        <v>8.67</v>
       </c>
       <c r="V8">
-        <v>1.201388888888889</v>
+        <v>0.2824104234527687</v>
       </c>
       <c r="W8">
-        <v>0.03638814016172507</v>
+        <v>-0.4473684210526315</v>
       </c>
       <c r="X8">
-        <v>0.08380625761744881</v>
+        <v>0.09349504618691791</v>
       </c>
       <c r="Y8">
-        <v>-0.04741811745572374</v>
+        <v>-0.5408634672395495</v>
       </c>
       <c r="Z8">
-        <v>0.1957845433255269</v>
+        <v>0</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06901414443312248</v>
+        <v>0.07696398678690015</v>
       </c>
       <c r="AC8">
-        <v>-0.06901414443312248</v>
+        <v>-0.07696398678690015</v>
       </c>
       <c r="AD8">
-        <v>57.7</v>
+        <v>45.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>57.7</v>
+        <v>45.7</v>
       </c>
       <c r="AG8">
-        <v>23.1</v>
+        <v>37.03</v>
       </c>
       <c r="AH8">
-        <v>0.6670520231213873</v>
+        <v>0.5981675392670157</v>
       </c>
       <c r="AI8">
-        <v>0.6527149321266968</v>
+        <v>0.8059964726631393</v>
       </c>
       <c r="AJ8">
-        <v>0.4450867052023121</v>
+        <v>0.5467296618928097</v>
       </c>
       <c r="AK8">
-        <v>0.429368029739777</v>
+        <v>0.7709764730376848</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1409,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIDAS Financing Limited (DSE:MIDASFIN)</t>
+          <t>DBH Finance PLC. (DSE:DBH)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1418,10 +1430,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0288</v>
+        <v>0.0211</v>
       </c>
       <c r="E9">
-        <v>0.0378</v>
+        <v>0.00026</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1436,28 +1448,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1.91</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L9">
-        <v>0.5276243093922651</v>
+        <v>0.4376884422110554</v>
       </c>
       <c r="M9">
-        <v>0.46</v>
+        <v>2.66</v>
       </c>
       <c r="N9">
-        <v>0.02541436464088398</v>
+        <v>0.02587548638132296</v>
       </c>
       <c r="O9">
-        <v>0.2408376963350786</v>
+        <v>0.3053960964408726</v>
       </c>
       <c r="P9">
-        <v>0.46</v>
+        <v>2.66</v>
       </c>
       <c r="Q9">
-        <v>0.02541436464088398</v>
+        <v>0.02587548638132296</v>
       </c>
       <c r="R9">
-        <v>0.2408376963350786</v>
+        <v>0.3053960964408726</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1466,55 +1478,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>6.35</v>
+        <v>196.2</v>
       </c>
       <c r="V9">
-        <v>0.3508287292817679</v>
+        <v>1.908560311284047</v>
       </c>
       <c r="W9">
-        <v>0.1364285714285714</v>
+        <v>0.112970168612192</v>
       </c>
       <c r="X9">
-        <v>0.07505664890679795</v>
+        <v>0.08245554522044046</v>
       </c>
       <c r="Y9">
-        <v>0.06137192252177348</v>
+        <v>0.03051462339175151</v>
       </c>
       <c r="Z9">
-        <v>0.1080597014925373</v>
+        <v>0.2979041916167665</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07036596409340401</v>
+        <v>0.07740666107716723</v>
       </c>
       <c r="AC9">
-        <v>-0.07036596409340401</v>
+        <v>-0.07740666107716723</v>
       </c>
       <c r="AD9">
-        <v>24</v>
+        <v>92.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>92.5</v>
       </c>
       <c r="AG9">
-        <v>17.65</v>
+        <v>-103.7</v>
       </c>
       <c r="AH9">
-        <v>0.5700712589073634</v>
+        <v>0.4736303123399898</v>
       </c>
       <c r="AI9">
-        <v>0.6451612903225806</v>
+        <v>0.5470136014192786</v>
       </c>
       <c r="AJ9">
-        <v>0.4937062937062937</v>
+        <v>115.2222222222233</v>
       </c>
       <c r="AK9">
-        <v>0.5721231766612642</v>
+        <v>3.826568265682657</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1531,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bay Leasing &amp; Investment Limited (DSE:BAYLEASING)</t>
+          <t>LankaBangla Finance PLC. (DSE:LANKABAFIN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1539,26 +1551,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>-0.0517</v>
+      </c>
+      <c r="E10">
+        <v>-0.166</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
       <c r="K10">
-        <v>-7</v>
+        <v>3.6</v>
+      </c>
+      <c r="L10">
+        <v>0.1168831168831169</v>
       </c>
       <c r="M10">
-        <v>1.19</v>
+        <v>5.33</v>
       </c>
       <c r="N10">
-        <v>0.0363914373088685</v>
+        <v>0.04173844949099452</v>
       </c>
       <c r="O10">
-        <v>-0.17</v>
+        <v>1.480555555555556</v>
       </c>
       <c r="P10">
-        <v>1.19</v>
+        <v>5.33</v>
       </c>
       <c r="Q10">
-        <v>0.0363914373088685</v>
+        <v>0.04173844949099452</v>
       </c>
       <c r="R10">
-        <v>-0.17</v>
+        <v>1.480555555555556</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1567,55 +1600,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>15</v>
+        <v>105.5</v>
       </c>
       <c r="V10">
-        <v>0.4587155963302752</v>
+        <v>0.8261550509005482</v>
       </c>
       <c r="W10">
-        <v>-0.1876675603217158</v>
+        <v>0.03422053231939164</v>
       </c>
       <c r="X10">
-        <v>0.0796145742893687</v>
+        <v>0.1008077117706415</v>
       </c>
       <c r="Y10">
-        <v>-0.2672821346110845</v>
+        <v>-0.06658717945124983</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07160132496173149</v>
+        <v>0.07799969899956075</v>
       </c>
       <c r="AC10">
-        <v>-0.07160132496173149</v>
+        <v>-0.07799969899956075</v>
       </c>
       <c r="AD10">
-        <v>54.9</v>
+        <v>239.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>54.9</v>
+        <v>239.9</v>
       </c>
       <c r="AG10">
-        <v>39.9</v>
+        <v>134.4</v>
       </c>
       <c r="AH10">
-        <v>0.6267123287671234</v>
+        <v>0.6526115342763874</v>
       </c>
       <c r="AI10">
-        <v>0.7065637065637065</v>
+        <v>0.7091339048182087</v>
       </c>
       <c r="AJ10">
-        <v>0.5495867768595042</v>
+        <v>0.5127813811522319</v>
       </c>
       <c r="AK10">
-        <v>0.6363636363636364</v>
+        <v>0.5773195876288659</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1632,7 +1665,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Premier Leasing &amp; Finance Limited (DSE:PREMIERLEA)</t>
+          <t>IDLC Finance PLC. (DSE:IDLC)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1640,26 +1673,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.0257</v>
+      </c>
+      <c r="E11">
+        <v>-0.0687</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
       <c r="K11">
-        <v>-24.1</v>
+        <v>14.6</v>
+      </c>
+      <c r="L11">
+        <v>0.3295711060948082</v>
       </c>
       <c r="M11">
-        <v>0.07099999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="N11">
-        <v>0.007959641255605381</v>
+        <v>0.03233125354509359</v>
       </c>
       <c r="O11">
-        <v>-0.002946058091286307</v>
+        <v>0.3904109589041096</v>
       </c>
       <c r="P11">
-        <v>0.07099999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="Q11">
-        <v>0.007959641255605381</v>
+        <v>0.03233125354509359</v>
       </c>
       <c r="R11">
-        <v>-0.002946058091286307</v>
+        <v>0.3904109589041096</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1668,55 +1722,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>23</v>
+        <v>279</v>
       </c>
       <c r="V11">
-        <v>2.57847533632287</v>
+        <v>1.58252977878616</v>
       </c>
       <c r="W11">
-        <v>-2.42211055276382</v>
+        <v>0.08400460299194476</v>
       </c>
       <c r="X11">
-        <v>0.1613060233884707</v>
+        <v>0.1058060112959422</v>
       </c>
       <c r="Y11">
-        <v>-2.58341657615229</v>
+        <v>-0.02180140830399742</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>0.1948109058927001</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07732069116540061</v>
+        <v>0.07855983231844664</v>
       </c>
       <c r="AC11">
-        <v>-0.07732069116540061</v>
+        <v>-0.07855983231844664</v>
       </c>
       <c r="AD11">
-        <v>71.40000000000001</v>
+        <v>378.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>71.40000000000001</v>
+        <v>378.2</v>
       </c>
       <c r="AG11">
-        <v>48.40000000000001</v>
+        <v>99.19999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.8889442231075697</v>
+        <v>0.6820559062218214</v>
       </c>
       <c r="AI11">
-        <v>1.18801996672213</v>
+        <v>0.6924203588429146</v>
       </c>
       <c r="AJ11">
-        <v>0.8443824145150035</v>
+        <v>0.3600725952813067</v>
       </c>
       <c r="AK11">
-        <v>1.304582210242587</v>
+        <v>0.3712574850299401</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1733,7 +1787,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FAS Finance &amp; Investment Limited (DSE:FASFIN)</t>
+          <t>United Finance Limited (DSE:UNITEDFIN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1741,26 +1795,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.0354</v>
+      </c>
+      <c r="E12">
+        <v>-0.166</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
       <c r="K12">
-        <v>-45.2</v>
+        <v>1.05</v>
+      </c>
+      <c r="L12">
+        <v>0.1557863501483679</v>
       </c>
       <c r="M12">
-        <v>0.004</v>
+        <v>0.887</v>
       </c>
       <c r="N12">
-        <v>0.0004756242568370987</v>
+        <v>0.03285185185185185</v>
       </c>
       <c r="O12">
-        <v>-8.849557522123894e-05</v>
+        <v>0.8447619047619047</v>
       </c>
       <c r="P12">
-        <v>0.004</v>
+        <v>0.887</v>
       </c>
       <c r="Q12">
-        <v>0.0004756242568370987</v>
+        <v>0.03285185185185185</v>
       </c>
       <c r="R12">
-        <v>-8.849557522123894e-05</v>
+        <v>0.8447619047619047</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1769,60 +1844,280 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>12.5</v>
+        <v>35.2</v>
       </c>
       <c r="V12">
-        <v>1.486325802615933</v>
+        <v>1.303703703703704</v>
       </c>
       <c r="W12">
-        <v>1.248618784530387</v>
+        <v>0.03420195439739414</v>
       </c>
       <c r="X12">
-        <v>0.1904553434071769</v>
+        <v>0.1142636402625338</v>
       </c>
       <c r="Y12">
-        <v>1.05816344112321</v>
+        <v>-0.08006168586513965</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>0.1252788104089219</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07780615428874865</v>
+        <v>0.07931849181354554</v>
       </c>
       <c r="AC12">
-        <v>-0.07780615428874865</v>
+        <v>-0.07931849181354554</v>
       </c>
       <c r="AD12">
-        <v>86.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>86.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AG12">
-        <v>73.8</v>
+        <v>34.89999999999999</v>
       </c>
       <c r="AH12">
-        <v>0.9112026185196918</v>
+        <v>0.7219361483007208</v>
       </c>
       <c r="AI12">
-        <v>8.460784313725487</v>
+        <v>0.7123983739837398</v>
       </c>
       <c r="AJ12">
-        <v>0.8977010096095366</v>
+        <v>0.5638126009693053</v>
       </c>
       <c r="AK12">
-        <v>-32.08695652173917</v>
+        <v>0.5522151898734177</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MIDAS Financing Limited (DSE:MIDASFIN)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.0711</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-1.9</v>
+      </c>
+      <c r="L13">
+        <v>-1.038251366120218</v>
+      </c>
+      <c r="M13">
+        <v>0.024</v>
+      </c>
+      <c r="N13">
+        <v>0.001714285714285714</v>
+      </c>
+      <c r="O13">
+        <v>-0.01263157894736842</v>
+      </c>
+      <c r="P13">
+        <v>0.024</v>
+      </c>
+      <c r="Q13">
+        <v>0.001714285714285714</v>
+      </c>
+      <c r="R13">
+        <v>-0.01263157894736842</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>4.84</v>
+      </c>
+      <c r="V13">
+        <v>0.3457142857142857</v>
+      </c>
+      <c r="W13">
+        <v>-0.143939393939394</v>
+      </c>
+      <c r="X13">
+        <v>0.09411057266777403</v>
+      </c>
+      <c r="Y13">
+        <v>-0.238049966607168</v>
+      </c>
+      <c r="Z13">
+        <v>0.0593192868719611</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.08064571684146062</v>
+      </c>
+      <c r="AC13">
+        <v>-0.08064571684146062</v>
+      </c>
+      <c r="AD13">
+        <v>21.3</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>21.3</v>
+      </c>
+      <c r="AG13">
+        <v>16.46</v>
+      </c>
+      <c r="AH13">
+        <v>0.6033994334277621</v>
+      </c>
+      <c r="AI13">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5403808273145109</v>
+      </c>
+      <c r="AK13">
+        <v>0.6174043510877719</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Premier Leasing &amp; Finance Limited (DSE:PREMIERLEA)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K14">
+        <v>-18.8</v>
+      </c>
+      <c r="M14">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="N14">
+        <v>0.01018181818181818</v>
+      </c>
+      <c r="O14">
+        <v>-0.004468085106382979</v>
+      </c>
+      <c r="P14">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.01018181818181818</v>
+      </c>
+      <c r="R14">
+        <v>-0.004468085106382979</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>20.2</v>
+      </c>
+      <c r="V14">
+        <v>2.448484848484848</v>
+      </c>
+      <c r="W14">
+        <v>1.504</v>
+      </c>
+      <c r="X14">
+        <v>0.2176249375620218</v>
+      </c>
+      <c r="Y14">
+        <v>1.286375062437978</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.08251982164918194</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08251982164918194</v>
+      </c>
+      <c r="AD14">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AG14">
+        <v>46.7</v>
+      </c>
+      <c r="AH14">
+        <v>0.8902195608782435</v>
+      </c>
+      <c r="AI14">
+        <v>1.581560283687943</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8498635122838945</v>
+      </c>
+      <c r="AK14">
+        <v>2.113122171945701</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
         <v>0</v>
       </c>
     </row>
